--- a/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flows\4 - Exercises\1 - Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADACCC14-E245-40EA-ABD9-61CB9541D735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A3DE1-0B4C-4C31-A8BC-9DC9F25A9608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -436,11 +436,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -448,19 +452,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -892,10 +892,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="51"/>
+      <c r="B1" s="48"/>
       <c r="C1" s="15" t="s">
         <v>25</v>
       </c>
@@ -913,10 +913,10 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="49"/>
       <c r="C2" s="12">
         <v>2000</v>
       </c>
@@ -940,10 +940,10 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="12">
         <v>1600</v>
       </c>
@@ -967,10 +967,10 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="49"/>
+      <c r="B4" s="51"/>
       <c r="C4" s="24">
         <v>100</v>
       </c>
@@ -994,10 +994,10 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="53"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="25">
         <f>C2-C3-C4</f>
         <v>300</v>
@@ -1021,10 +1021,10 @@
       <c r="L5" s="17"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="49"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="26">
         <f>(J17+J21)*$J$3</f>
         <v>9</v>
@@ -1046,13 +1046,13 @@
         <v>3</v>
       </c>
       <c r="H6" s="16"/>
-      <c r="I6" s="54"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="48"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="25">
         <f>C5-C6</f>
         <v>291</v>
@@ -1075,10 +1075,10 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="49"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="24">
         <f>C7*$J$2</f>
         <v>87.3</v>
@@ -1102,10 +1102,10 @@
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="50"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="27">
         <f>C7-C8</f>
         <v>203.7</v>
@@ -1128,10 +1128,10 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="46"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="25">
         <f>C9*(1-$J$4)</f>
         <v>81.48</v>
@@ -1156,10 +1156,10 @@
       <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="46"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="25">
         <f>C9*$J$4</f>
         <v>122.21999999999998</v>
@@ -1253,27 +1253,27 @@
       </c>
       <c r="B16" s="28">
         <f>J29-(B17+B18+B26)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16" s="28">
         <f>K29-(C17+C18+C26)</f>
-        <v>131.48000000000002</v>
+        <v>231.48000000000002</v>
       </c>
       <c r="D16" s="28">
         <f>L29-(D17+D18+D26)</f>
-        <v>312.96000000000004</v>
+        <v>412.96000000000004</v>
       </c>
       <c r="E16" s="28">
         <f>M29-(E17+E18+E26)</f>
-        <v>494.44000000000005</v>
+        <v>594.44000000000005</v>
       </c>
       <c r="F16" s="28">
         <f t="shared" ref="F16:G16" si="10">N29-(F17+F18+F26)</f>
-        <v>675.92000000000007</v>
+        <v>775.92000000000007</v>
       </c>
       <c r="G16" s="28">
         <f t="shared" si="10"/>
-        <v>609.08000000000004</v>
+        <v>709.08</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="6" t="s">
@@ -1394,27 +1394,27 @@
       </c>
       <c r="B19" s="28">
         <f>SUM(B16:B18)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19" s="28">
         <f t="shared" ref="C19:E19" si="11">SUM(C16:C18)</f>
-        <v>331.48</v>
+        <v>431.48</v>
       </c>
       <c r="D19" s="28">
         <f t="shared" si="11"/>
-        <v>512.96</v>
+        <v>612.96</v>
       </c>
       <c r="E19" s="28">
         <f t="shared" si="11"/>
-        <v>694.44</v>
+        <v>794.44</v>
       </c>
       <c r="F19" s="28">
         <f t="shared" ref="F19:G19" si="12">SUM(F16:F18)</f>
-        <v>875.92000000000007</v>
+        <v>975.92000000000007</v>
       </c>
       <c r="G19" s="28">
         <f t="shared" si="12"/>
-        <v>609.08000000000004</v>
+        <v>709.08</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>7</v>
@@ -1535,22 +1535,22 @@
         <v>41</v>
       </c>
       <c r="J24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O24" s="25">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.45">
@@ -1640,27 +1640,27 @@
       </c>
       <c r="J26" s="36">
         <f>J24+J25</f>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K26" s="36">
         <f t="shared" ref="K26:M26" si="26">K24+K25</f>
-        <v>281.48</v>
+        <v>381.48</v>
       </c>
       <c r="L26" s="36">
         <f t="shared" si="26"/>
-        <v>362.96000000000004</v>
+        <v>462.96000000000004</v>
       </c>
       <c r="M26" s="36">
         <f t="shared" si="26"/>
-        <v>444.44</v>
+        <v>544.44000000000005</v>
       </c>
       <c r="N26" s="36">
         <f t="shared" ref="N26:O26" si="27">N24+N25</f>
-        <v>525.92000000000007</v>
+        <v>625.92000000000007</v>
       </c>
       <c r="O26" s="36">
         <f t="shared" si="27"/>
-        <v>609.08000000000004</v>
+        <v>709.08</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.45">
@@ -1677,54 +1677,54 @@
       </c>
       <c r="B29" s="37">
         <f>B19+B26</f>
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C29" s="37">
         <f>C19+C26</f>
-        <v>731.48</v>
+        <v>831.48</v>
       </c>
       <c r="D29" s="37">
         <f>D19+D26</f>
-        <v>812.96</v>
+        <v>912.96</v>
       </c>
       <c r="E29" s="37">
         <f>E19+E26</f>
-        <v>894.44</v>
+        <v>994.44</v>
       </c>
       <c r="F29" s="37">
         <f t="shared" ref="F29:G29" si="28">F19+F26</f>
-        <v>975.92000000000007</v>
+        <v>1075.92</v>
       </c>
       <c r="G29" s="37">
         <f t="shared" si="28"/>
-        <v>609.08000000000004</v>
+        <v>709.08</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="38">
         <f>J22+J26</f>
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K29" s="38">
         <f>K22+K26</f>
-        <v>731.48</v>
+        <v>831.48</v>
       </c>
       <c r="L29" s="38">
         <f>L22+L26</f>
-        <v>812.96</v>
+        <v>912.96</v>
       </c>
       <c r="M29" s="38">
         <f>M22+M26</f>
-        <v>894.44</v>
+        <v>994.44</v>
       </c>
       <c r="N29" s="38">
         <f t="shared" ref="N29:O29" si="29">N22+N26</f>
-        <v>975.92000000000007</v>
+        <v>1075.92</v>
       </c>
       <c r="O29" s="38">
         <f t="shared" si="29"/>
-        <v>609.08000000000004</v>
+        <v>709.08</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">

--- a/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A3DE1-0B4C-4C31-A8BC-9DC9F25A9608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897CCD1A-3492-40BD-8CEA-A7823AC99FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="65">
   <si>
     <t>Cash</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Sales is projected to be $2000 with a gross profit margin of 20% (i.e. $1,600 in COGS) in years 1 through 5.</t>
+  </si>
+  <si>
+    <t>=EBIT</t>
   </si>
 </sst>
 </file>
@@ -369,7 +372,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -459,6 +462,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -994,8 +1000,8 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="52" t="s">
-        <v>18</v>
+      <c r="A5" s="55" t="s">
+        <v>64</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="25">

--- a/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow Review - Solutions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897CCD1A-3492-40BD-8CEA-A7823AC99FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4924A2BB-2EBA-4A5B-A9FD-02508B1B3BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
@@ -455,6 +455,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -462,9 +465,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1000,10 +1000,10 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="52"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="25">
         <f>C2-C3-C4</f>
         <v>300</v>
@@ -1032,24 +1032,24 @@
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="26">
-        <f>(J17+J21)*$J$3</f>
+        <f>(J17+J18+J21)*$J$3</f>
         <v>9</v>
       </c>
       <c r="D6" s="26">
-        <f>(K17+K21)*$J$3</f>
+        <f t="shared" ref="D6:G6" si="2">(K17+K18+K21)*$J$3</f>
         <v>9</v>
       </c>
       <c r="E6" s="26">
-        <f>(L17+L21)*$J$3</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F6" s="26">
-        <f t="shared" ref="F6:G6" si="2">(M17+M21)*$J$3</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="G6" s="26">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="46"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G7" s="25">
         <f t="shared" si="4"/>
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
@@ -1103,15 +1103,15 @@
       </c>
       <c r="G8" s="24">
         <f t="shared" si="5"/>
-        <v>89.1</v>
+        <v>87.3</v>
       </c>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="27">
         <f>C7-C8</f>
         <v>203.7</v>
@@ -1130,14 +1130,14 @@
       </c>
       <c r="G9" s="27">
         <f t="shared" si="7"/>
-        <v>207.9</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="53"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="25">
         <f>C9*(1-$J$4)</f>
         <v>81.48</v>
@@ -1156,16 +1156,16 @@
       </c>
       <c r="G10" s="25">
         <f t="shared" si="8"/>
-        <v>83.160000000000011</v>
+        <v>81.48</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="53"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="25">
         <f>C9*$J$4</f>
         <v>122.21999999999998</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G11" s="25">
         <f t="shared" si="9"/>
-        <v>124.74</v>
+        <v>122.21999999999998</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="G16" s="28">
         <f t="shared" si="10"/>
-        <v>709.08</v>
+        <v>707.40000000000009</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="6" t="s">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G19" s="28">
         <f t="shared" si="12"/>
-        <v>709.08</v>
+        <v>707.40000000000009</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>7</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="O25" s="35">
         <f t="shared" si="23"/>
-        <v>409.08000000000004</v>
+        <v>407.40000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="O26" s="36">
         <f t="shared" si="27"/>
-        <v>709.08</v>
+        <v>707.40000000000009</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.45">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G29" s="37">
         <f t="shared" si="28"/>
-        <v>709.08</v>
+        <v>707.40000000000009</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>13</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="O29" s="38">
         <f t="shared" si="29"/>
-        <v>709.08</v>
+        <v>707.40000000000009</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
